--- a/sample-imports/storage-locations/storage_locations_sample.xlsx
+++ b/sample-imports/storage-locations/storage_locations_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,24 +443,168 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Freezer A - Shelf 2</t>
+          <t>Cold Room 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-20°C freezer, shelf 2</t>
+          <t>4°C overflow sample storage</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Freezer A - Shelf 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-20°C freezer, shelf 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Freezer A - Shelf 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-20°C freezer, shelf 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Freezer B - Shelf 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-80°C ultra-low freezer, shelf 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reagent Cabinet 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ambient storage for general reagents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reagent Cabinet 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ambient storage for flammable reagents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Reagent Cabinet 3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ambient storage for reagents</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ambient storage for corrosive reagents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Retention Sample Room</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Long-term retention sample storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Standards Vault</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Secure storage for reference standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QC Sample Shelf 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quality control retained samples, shelf 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QC Sample Shelf 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quality control retained samples, shelf 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Glassware Storage</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cleaned glassware storage cabinet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Waste Holding Area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Temporary chemical waste holding area</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Archive Room</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Archived sample and document storage</t>
         </is>
       </c>
     </row>
